--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5900</v>
+        <v>7171</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>387</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7171</v>
+        <v>16881</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>433</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16881</v>
+        <v>33117</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>496</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33117</v>
+        <v>47902</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>541</v>
+        <v>556</v>
       </c>
     </row>
     <row r="4">

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47902</v>
+        <v>47908</v>
       </c>
     </row>
     <row r="3">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47908</v>
+        <v>56524</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>556</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56524</v>
+        <v>22759</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>566</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22759</v>
+        <v>57769</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>526</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57769</v>
+        <v>58624</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
